--- a/sheets/민요/검수/석별가.xlsx
+++ b/sheets/민요/검수/석별가.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,54 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2609,8 +2737,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:M14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -2625,388 +2757,321 @@
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">석별가 — 민요채보-2/석별가.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">석별가</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢
 黃</t>
         </is>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="C3" s="17"/>
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">夾
 南</t>
         </is>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="E3" s="17"/>
+      <c r="F3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="G3" s="17"/>
+      <c r="H3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="I3" s="17"/>
+      <c r="J3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 汰</t>
         </is>
       </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="K3" s="17"/>
+      <c r="L3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">夾
 夾</t>
         </is>
       </c>
-      <c r="M3" s="3"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="M3" s="17"/>
+    </row>
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="C4" s="18"/>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E4" s="18"/>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G4" s="18"/>
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I4" s="18"/>
+      <c r="J4" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="K4" s="18"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="19"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="16"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="I5" s="21"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M5" s="3"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="M5" s="21"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 夾</t>
         </is>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="C6" s="17"/>
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 夾</t>
         </is>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="E6" s="17"/>
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="G6" s="17"/>
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="I6" s="17"/>
+      <c r="J6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K6" s="17"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="22"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="16"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="19"/>
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 夾</t>
         </is>
       </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="G7" s="18"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K7" s="18"/>
+      <c r="L7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 汰</t>
         </is>
       </c>
-      <c r="M7" s="3"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="M7" s="18"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="C8" s="20"/>
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 夾</t>
         </is>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" s="21"/>
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G8" s="20"/>
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="I8" s="20"/>
+      <c r="J8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="K8" s="21"/>
+      <c r="L8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="M8" s="21"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="C9" s="17"/>
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="E9" s="17"/>
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="G9" s="17"/>
+      <c r="H9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰
 潢</t>
         </is>
       </c>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="I9" s="17"/>
+      <c r="J9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K9" s="3"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-    </row>
-    <row r="10" ht="64" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="K9" s="17"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="22"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="16"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢
 汰</t>
         </is>
       </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="E10" s="18"/>
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰
 潢</t>
         </is>
       </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="G10" s="18"/>
+      <c r="H10" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰
@@ -3014,169 +3079,221 @@
 無</t>
         </is>
       </c>
-      <c r="I10" s="3"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="I10" s="18"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="19"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C11" s="20"/>
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 無</t>
         </is>
       </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="E11" s="21"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="I11" s="20"/>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 汰</t>
-        </is>
-      </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="K11" s="20"/>
+      <c r="L11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="M11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="M11" s="20"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="C12" s="17"/>
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="E12" s="17"/>
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="G12" s="17"/>
+      <c r="H12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="I12" s="17"/>
+      <c r="J12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="K12" s="17"/>
+      <c r="L12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="M12" s="17"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C13" s="19"/>
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="E13" s="19"/>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G13" s="18"/>
+      <c r="H13" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 夾</t>
         </is>
       </c>
-      <c r="I13" s="3"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="I13" s="18"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="M13" s="18"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" s="20"/>
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">夾
 △</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="E14" s="20"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="I14" s="20"/>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
+          </r>
+        </is>
+      </c>
+      <c r="K14" s="20"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="20"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:M2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="100"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/석별가.xlsx
+++ b/sheets/민요/검수/석별가.xlsx
@@ -365,7 +365,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">인쇄된 12정간 양식(굵은 선 3칸마다 → 3/4, 용지 번호 "- 197 -"). 위 줄 번호 오른쪽부터 1, 왼쪽에 정간 1~12. 오른쪽 여백에 제목 "석별가"와 장단 "굿거리"를 세로로 적어 둠. 내용 있는 줄은 오른쪽 6줄(7~8줄은 빔). 각 율명 줄 오른쪽 좁은 칸에 손글씨 가사가 있어 그대로 전사함(5번째 줄 후렴 "가세 가세 나도 가세"가 가장 또렷함). 청황 潢·청태 汰·청림 淋·중성 南/姑가 지배적. 정간8~9에 율명이 2~3자 쌓여 있고 정간12는 종지 꾸밈(―/○)으로 보임. 흘림체가 심해 일부 가사·율명은 비고에 불확실 표시. AI 재판독.</t>
+          <t xml:space="preserve">인쇄된 12정간 양식(굵은 선 3칸마다 → 3/4, 용지 번호 "- 197 -"). 위 줄 번호 오른쪽부터 1, 왼쪽에 정간 1~12. 오른쪽 여백에 제목 "석별가"와 장단 "굿거리"를 세로로 적어 둠. 내용 있는 줄은 오른쪽 6줄(7~8줄은 빔). 각 율명 줄 오른쪽 좁은 칸에 손글씨 가사가 있어 그대로 전사함(5번째 줄 후렴 "가세 가세 나도 가세"가 가장 또렷함). 청황 潢·청태 汰·청림 淋·중성 南/姑가 지배적. 정간8~9에 율명이 2~3자 쌓여 있고 정간12는 종지 꾸밈(–/○)으로 보임. 흘림체가 심해 일부 가사·율명은 비고에 불확실 표시. AI 재판독.</t>
         </is>
       </c>
     </row>
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|汰</t>
+          <t xml:space="preserve">–|汰</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -913,12 +913,12 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I11" s="3"/>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I15" s="2"/>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I22" s="2"/>
@@ -1786,12 +1786,12 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I34" s="2"/>
@@ -2842,12 +2842,12 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|潢</t>
+          <t xml:space="preserve">–|潢</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -2984,12 +2984,12 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -3359,7 +3359,7 @@
       <c r="A7" s="0"/>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K7" s="9"/>
@@ -3573,7 +3573,7 @@
       <c r="A11" s="0"/>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -3612,7 +3612,7 @@
       <c r="K11" s="10"/>
       <c r="L11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -3750,19 +3750,19 @@
       </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I14" s="10"/>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K14" s="10"/>
       <c r="L14" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M14" s="13"/>

--- a/sheets/민요/검수/석별가.xlsx
+++ b/sheets/민요/검수/석별가.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3134,77 +3175,77 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">석별가</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="C3" s="22"/>
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">그</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="J3" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K3" s="11" t="inlineStr">
+      <c r="J3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">거</t>
         </is>
@@ -3212,42 +3253,42 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="25"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="18" t="inlineStr">
+      <c r="G4" s="25"/>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I4" s="25"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M4" s="12" t="inlineStr">
+      <c r="M4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">닌</t>
         </is>
@@ -3255,101 +3296,101 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="27"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="27"/>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">의</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="I5" s="27"/>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
-      <c r="L5" s="17"/>
-      <c r="M5" s="10"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="27"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C6" s="22"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑^</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">말</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">정</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">임</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">금</t>
         </is>
@@ -3357,92 +3398,92 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="25"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="G7" s="25"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢^</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="9"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="25"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="27"/>
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="27"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑^</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="I8" s="27"/>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K8" s="27"/>
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰^</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="M8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">면</t>
         </is>
@@ -3450,58 +3491,58 @@
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="C9" s="22"/>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">엿</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">걸</t>
         </is>
       </c>
-      <c r="L9" s="18" t="inlineStr">
+      <c r="L9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M9" s="11" t="inlineStr">
+      <c r="M9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">돈</t>
         </is>
@@ -3509,61 +3550,61 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="25"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="I10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">었</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="K10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="L10" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M10" s="12" t="inlineStr">
+      <c r="L10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">질</t>
         </is>
@@ -3571,52 +3612,52 @@
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="C11" s="27"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="G11" s="27"/>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="I11" s="27"/>
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="K11" s="27"/>
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -3624,58 +3665,58 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="22"/>
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">말</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">두</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰^</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -3683,89 +3724,89 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="25"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="E13" s="25"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑^</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M13" s="9"/>
+      <c r="M13" s="25"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">○</t>
         </is>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="C14" s="28"/>
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">○</t>
         </is>
       </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="28"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="I14" s="27"/>
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="18" t="inlineStr">
+      <c r="K14" s="27"/>
+      <c r="L14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M14" s="13"/>
+      <c r="M14" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/석별가.xlsx
+++ b/sheets/민요/검수/석별가.xlsx
@@ -3156,24 +3156,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G4" s="25"/>
@@ -3294,17 +3294,17 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C5" s="27"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E5" s="27"/>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I5" s="27"/>
@@ -3337,7 +3337,7 @@
       <c r="L5" s="21"/>
       <c r="M5" s="27"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G7" s="25"/>
@@ -3440,7 +3440,7 @@
       <c r="L7" s="21"/>
       <c r="M7" s="25"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I8" s="27"/>
@@ -3489,7 +3489,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3722,17 +3722,17 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C13" s="25"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E13" s="25"/>
@@ -3760,12 +3760,12 @@
       </c>
       <c r="L13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>

--- a/sheets/민요/검수/석별가.xlsx
+++ b/sheets/민요/검수/석별가.xlsx
@@ -2704,12 +2704,12 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I57" s="3"/>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I69" s="3"/>
@@ -3769,13 +3769,13 @@
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C14" s="28"/>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">○</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E14" s="28"/>

--- a/sheets/민요/검수/석별가.xlsx
+++ b/sheets/민요/검수/석별가.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3199,13 +3222,13 @@
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="C3" s="22"/>
+      <c r="C3" s="29"/>
       <c r="D3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="E3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -3215,7 +3238,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">그</t>
         </is>
@@ -3225,7 +3248,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -3235,7 +3258,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K3" s="24" t="inlineStr">
+      <c r="K3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -3245,7 +3268,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M3" s="22" t="inlineStr">
+      <c r="M3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">거</t>
         </is>
@@ -3258,13 +3281,13 @@
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="C4" s="25"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
@@ -3274,21 +3297,21 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G4" s="25"/>
+      <c r="G4" s="31"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I4" s="25"/>
+      <c r="I4" s="31"/>
       <c r="J4" s="21"/>
-      <c r="K4" s="25"/>
+      <c r="K4" s="31"/>
       <c r="L4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M4" s="26" t="inlineStr">
+      <c r="M4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">닌</t>
         </is>
@@ -3301,19 +3324,19 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="27"/>
+      <c r="C5" s="33"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E5" s="27"/>
+      <c r="E5" s="33"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="G5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">의</t>
         </is>
@@ -3323,19 +3346,19 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="27"/>
+      <c r="I5" s="33"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K5" s="27" t="inlineStr">
+      <c r="K5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
       <c r="L5" s="21"/>
-      <c r="M5" s="27"/>
+      <c r="M5" s="33"/>
     </row>
     <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
@@ -3344,13 +3367,13 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C6" s="22"/>
+      <c r="C6" s="29"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -3360,7 +3383,7 @@
           <t xml:space="preserve">姑^</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">말</t>
         </is>
@@ -3370,7 +3393,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">정</t>
         </is>
@@ -3380,7 +3403,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr">
+      <c r="K6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">임</t>
         </is>
@@ -3390,7 +3413,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M6" s="22" t="inlineStr">
+      <c r="M6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">금</t>
         </is>
@@ -3404,13 +3427,13 @@
 潢</t>
         </is>
       </c>
-      <c r="C7" s="25"/>
+      <c r="C7" s="31"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
@@ -3420,13 +3443,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G7" s="25"/>
+      <c r="G7" s="31"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢^</t>
         </is>
       </c>
-      <c r="I7" s="25" t="inlineStr">
+      <c r="I7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
@@ -3436,9 +3459,9 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K7" s="25"/>
+      <c r="K7" s="31"/>
       <c r="L7" s="21"/>
-      <c r="M7" s="25"/>
+      <c r="M7" s="31"/>
     </row>
     <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
@@ -3448,20 +3471,20 @@
 無</t>
         </is>
       </c>
-      <c r="C8" s="27"/>
+      <c r="C8" s="33"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E8" s="27"/>
+      <c r="E8" s="33"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑^</t>
         </is>
       </c>
-      <c r="G8" s="27" t="inlineStr">
+      <c r="G8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -3471,19 +3494,19 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I8" s="27"/>
+      <c r="I8" s="33"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K8" s="27"/>
+      <c r="K8" s="33"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰^</t>
         </is>
       </c>
-      <c r="M8" s="27" t="inlineStr">
+      <c r="M8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">면</t>
         </is>
@@ -3496,13 +3519,13 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C9" s="22"/>
+      <c r="C9" s="29"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -3512,7 +3535,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
@@ -3522,7 +3545,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">엿</t>
         </is>
@@ -3532,7 +3555,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">걸</t>
         </is>
@@ -3542,7 +3565,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M9" s="24" t="inlineStr">
+      <c r="M9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">돈</t>
         </is>
@@ -3555,14 +3578,14 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C10" s="25"/>
+      <c r="C10" s="31"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
@@ -3572,7 +3595,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G10" s="25" t="inlineStr">
+      <c r="G10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
@@ -3583,7 +3606,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I10" s="25" t="inlineStr">
+      <c r="I10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">었</t>
         </is>
@@ -3594,7 +3617,7 @@
 潢</t>
         </is>
       </c>
-      <c r="K10" s="25" t="inlineStr">
+      <c r="K10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -3604,7 +3627,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M10" s="26" t="inlineStr">
+      <c r="M10" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">질</t>
         </is>
@@ -3618,14 +3641,14 @@
 無</t>
         </is>
       </c>
-      <c r="C11" s="27"/>
+      <c r="C11" s="33"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E11" s="27" t="inlineStr">
+      <c r="E11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -3636,28 +3659,28 @@
 無</t>
         </is>
       </c>
-      <c r="G11" s="27"/>
+      <c r="G11" s="33"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I11" s="27"/>
+      <c r="I11" s="33"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K11" s="27"/>
+      <c r="K11" s="33"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="M11" s="27" t="inlineStr">
+      <c r="M11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -3670,13 +3693,13 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="22"/>
+      <c r="C12" s="29"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
@@ -3686,7 +3709,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">말</t>
         </is>
@@ -3696,7 +3719,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
@@ -3706,7 +3729,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">두</t>
         </is>
@@ -3716,7 +3739,7 @@
           <t xml:space="preserve">汰^</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr">
+      <c r="M12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -3729,21 +3752,21 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="25"/>
+      <c r="C13" s="31"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E13" s="25"/>
+      <c r="E13" s="31"/>
       <c r="F13" s="21"/>
-      <c r="G13" s="25"/>
+      <c r="G13" s="31"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I13" s="25" t="inlineStr">
+      <c r="I13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -3753,7 +3776,7 @@
           <t xml:space="preserve">姑^</t>
         </is>
       </c>
-      <c r="K13" s="25" t="inlineStr">
+      <c r="K13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -3763,7 +3786,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M13" s="25"/>
+      <c r="M13" s="31"/>
     </row>
     <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
@@ -3772,19 +3795,19 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="C14" s="28"/>
+      <c r="C14" s="34"/>
       <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="E14" s="28"/>
+      <c r="E14" s="34"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G14" s="27" t="inlineStr">
+      <c r="G14" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -3794,19 +3817,19 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I14" s="27"/>
+      <c r="I14" s="33"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K14" s="27"/>
+      <c r="K14" s="33"/>
       <c r="L14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M14" s="28"/>
+      <c r="M14" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/석별가.xlsx
+++ b/sheets/민요/검수/석별가.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -223,40 +218,22 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -319,11 +296,7 @@
           <t xml:space="preserve">쪽</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197</t>
-        </is>
-      </c>
+      <c r="B5" s="4"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -357,7 +330,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">68</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
     </row>
@@ -369,7 +342,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
     </row>
@@ -429,7 +402,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">인쇄된 12정간 양식(굵은 선 3칸마다 → 3/4, 용지 번호 "- 197 -"). 위 줄 번호 오른쪽부터 1, 왼쪽에 정간 1~12. 오른쪽 여백에 제목 "석별가"와 장단 "굿거리"를 세로로 적어 둠. 내용 있는 줄은 오른쪽 6줄(7~8줄은 빔). 각 율명 줄 오른쪽 좁은 칸에 손글씨 가사가 있어 그대로 전사함(5번째 줄 후렴 "가세 가세 나도 가세"가 가장 또렷함). 청황 潢·청태 汰·청림 淋·중성 南/姑가 지배적. 정간8~9에 율명이 2~3자 쌓여 있고 정간12는 종지 꾸밈(–/○)으로 보임. 흘림체가 심해 일부 가사·율명은 비고에 불확실 표시. AI 재판독.</t>
+          <t xml:space="preserve">10-13 전면 재판독(이전 판독은 율명·가사 위치가 원본과 달랐음). 인쇄 12정간 양식, 굵은 선 3칸마다 → 3/4. 오른쪽부터 6줄(7·8줄 빔). 가사는 각 율명 줄 오른쪽 칸. 정간12 의 –와 ▷ 모양은 –|△ 로 적음. 율명 오른쪽 ^ 꾸밈은 ^ 로 적음.</t>
         </is>
       </c>
     </row>
@@ -617,17 +590,17 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">거</t>
+          <t xml:space="preserve">가</t>
         </is>
       </c>
       <c r="J2" s="4"/>
@@ -654,26 +627,22 @@
       <c r="F3" s="2">
         <v>1</v>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">닌</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">청태</t>
-        </is>
-      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑^</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑^</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">련</t>
+        </is>
+      </c>
+      <c r="J3" s="4"/>
       <c r="K3" s="2"/>
     </row>
     <row r="4">
@@ -699,17 +668,17 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">금</t>
+          <t xml:space="preserve">한</t>
         </is>
       </c>
       <c r="J4" s="4"/>
@@ -731,24 +700,24 @@
         <v>1</v>
       </c>
       <c r="E5" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2">
         <v>2</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰^</t>
+          <t xml:space="preserve">南^</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰^</t>
+          <t xml:space="preserve">南^</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">면</t>
+          <t xml:space="preserve">님</t>
         </is>
       </c>
       <c r="J5" s="4"/>
@@ -775,26 +744,22 @@
       <c r="F6" s="2">
         <v>3</v>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">돈</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">청중(氵仲)로 봄</t>
-        </is>
-      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+      <c r="J6" s="4"/>
       <c r="K6" s="2"/>
     </row>
     <row r="7">
@@ -818,26 +783,22 @@
       <c r="F7" s="2">
         <v>3</v>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">질</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사 질/일?</t>
-        </is>
-      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">별</t>
+        </is>
+      </c>
+      <c r="J7" s="4"/>
       <c r="K7" s="2"/>
     </row>
     <row r="8">
@@ -863,401 +824,401 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">–|姑</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+姑</t>
+        </is>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2">
+        <v>1</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/석별가.png</t>
+        </is>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <v>10</v>
+      </c>
+      <c r="F9" s="2">
+        <v>4</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+      <c r="J9" s="4"/>
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2">
+        <v>1</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/석별가.png</t>
+        </is>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
+        <v>11</v>
+      </c>
+      <c r="F10" s="2">
+        <v>4</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
+      <c r="J10" s="4"/>
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2">
+        <v>1</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/석별가.png</t>
+        </is>
+      </c>
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>12</v>
+      </c>
+      <c r="F11" s="2">
+        <v>4</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I11" s="2"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2">
+        <v>1</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/석별가.png</t>
+        </is>
+      </c>
+      <c r="C12" s="2">
+        <v>2</v>
+      </c>
+      <c r="D12" s="2">
+        <v>2</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">거</t>
+        </is>
+      </c>
+      <c r="J12" s="4"/>
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2">
+        <v>1</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/석별가.png</t>
+        </is>
+      </c>
+      <c r="C13" s="2">
+        <v>2</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2">
+        <v>2</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">년</t>
+        </is>
+      </c>
+      <c r="J13" s="4"/>
+      <c r="K13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2">
+        <v>1</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/석별가.png</t>
+        </is>
+      </c>
+      <c r="C14" s="2">
+        <v>2</v>
+      </c>
+      <c r="D14" s="2">
+        <v>2</v>
+      </c>
+      <c r="E14" s="2">
+        <v>4</v>
+      </c>
+      <c r="F14" s="2">
+        <v>2</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">금</t>
+        </is>
+      </c>
+      <c r="J14" s="4"/>
+      <c r="K14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2">
+        <v>1</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/석별가.png</t>
+        </is>
+      </c>
+      <c r="C15" s="2">
+        <v>2</v>
+      </c>
+      <c r="D15" s="2">
+        <v>2</v>
+      </c>
+      <c r="E15" s="2">
+        <v>6</v>
+      </c>
+      <c r="F15" s="2">
+        <v>2</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰^</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰^</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">년</t>
+        </is>
+      </c>
+      <c r="J15" s="4"/>
+      <c r="K15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2">
+        <v>1</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/석별가.png</t>
+        </is>
+      </c>
+      <c r="C16" s="2">
+        <v>2</v>
+      </c>
+      <c r="D16" s="2">
+        <v>2</v>
+      </c>
+      <c r="E16" s="2">
+        <v>7</v>
+      </c>
+      <c r="F16" s="2">
+        <v>3</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">돈</t>
+        </is>
+      </c>
+      <c r="J16" s="4"/>
+      <c r="K16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2">
+        <v>1</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/석별가.png</t>
+        </is>
+      </c>
+      <c r="C17" s="2">
+        <v>2</v>
+      </c>
+      <c r="D17" s="2">
+        <v>2</v>
+      </c>
+      <c r="E17" s="2">
+        <v>8</v>
+      </c>
+      <c r="F17" s="2">
+        <v>3</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">절</t>
+        </is>
+      </c>
+      <c r="J17" s="4"/>
+      <c r="K17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2">
+        <v>1</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/석별가.png</t>
+        </is>
+      </c>
+      <c r="C18" s="2">
+        <v>2</v>
+      </c>
+      <c r="D18" s="2">
+        <v>2</v>
+      </c>
+      <c r="E18" s="2">
+        <v>9</v>
+      </c>
+      <c r="F18" s="2">
+        <v>3</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">–|汰</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
-        </is>
-      </c>
-      <c r="J8" s="4"/>
-      <c r="K8" s="2"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2">
-        <v>1</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/석별가.png</t>
-        </is>
-      </c>
-      <c r="C9" s="2">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2">
-        <v>10</v>
-      </c>
-      <c r="F9" s="2">
-        <v>4</v>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰^</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰^</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
-      <c r="J9" s="4"/>
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2">
-        <v>1</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/석별가.png</t>
-        </is>
-      </c>
-      <c r="C10" s="2">
-        <v>1</v>
-      </c>
-      <c r="D10" s="2">
-        <v>1</v>
-      </c>
-      <c r="E10" s="2">
-        <v>11</v>
-      </c>
-      <c r="F10" s="2">
-        <v>4</v>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2">
-        <v>1</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/석별가.png</t>
-        </is>
-      </c>
-      <c r="C11" s="2">
-        <v>1</v>
-      </c>
-      <c r="D11" s="2">
-        <v>1</v>
-      </c>
-      <c r="E11" s="2">
-        <v>12</v>
-      </c>
-      <c r="F11" s="2">
-        <v>4</v>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I11" s="3"/>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간12 종지 꾸밈</t>
-        </is>
-      </c>
-      <c r="K11" s="2"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2">
-        <v>1</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/석별가.png</t>
-        </is>
-      </c>
-      <c r="C12" s="2">
-        <v>2</v>
-      </c>
-      <c r="D12" s="2">
-        <v>2</v>
-      </c>
-      <c r="E12" s="2">
-        <v>1</v>
-      </c>
-      <c r="F12" s="2">
-        <v>1</v>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">고</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">청황</t>
-        </is>
-      </c>
-      <c r="K12" s="2"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2">
-        <v>1</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/석별가.png</t>
-        </is>
-      </c>
-      <c r="C13" s="2">
-        <v>2</v>
-      </c>
-      <c r="D13" s="2">
-        <v>2</v>
-      </c>
-      <c r="E13" s="2">
-        <v>3</v>
-      </c>
-      <c r="F13" s="2">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">은</t>
-        </is>
-      </c>
-      <c r="J13" s="4"/>
-      <c r="K13" s="2"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2">
-        <v>1</v>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/석별가.png</t>
-        </is>
-      </c>
-      <c r="C14" s="2">
-        <v>2</v>
-      </c>
-      <c r="D14" s="2">
-        <v>2</v>
-      </c>
-      <c r="E14" s="2">
-        <v>4</v>
-      </c>
-      <c r="F14" s="2">
-        <v>2</v>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">임</t>
-        </is>
-      </c>
-      <c r="J14" s="4"/>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2">
-        <v>1</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/석별가.png</t>
-        </is>
-      </c>
-      <c r="C15" s="2">
-        <v>2</v>
-      </c>
-      <c r="D15" s="2">
-        <v>2</v>
-      </c>
-      <c r="E15" s="2">
-        <v>5</v>
-      </c>
-      <c r="F15" s="2">
-        <v>2</v>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="2"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2">
-        <v>1</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/석별가.png</t>
-        </is>
-      </c>
-      <c r="C16" s="2">
-        <v>2</v>
-      </c>
-      <c r="D16" s="2">
-        <v>2</v>
-      </c>
-      <c r="E16" s="2">
-        <v>6</v>
-      </c>
-      <c r="F16" s="2">
-        <v>2</v>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2">
-        <v>1</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/석별가.png</t>
-        </is>
-      </c>
-      <c r="C17" s="2">
-        <v>2</v>
-      </c>
-      <c r="D17" s="2">
-        <v>2</v>
-      </c>
-      <c r="E17" s="2">
-        <v>7</v>
-      </c>
-      <c r="F17" s="2">
-        <v>3</v>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">걸</t>
-        </is>
-      </c>
-      <c r="J17" s="4"/>
-      <c r="K17" s="2"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2">
-        <v>1</v>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/석별가.png</t>
-        </is>
-      </c>
-      <c r="C18" s="2">
-        <v>2</v>
-      </c>
-      <c r="D18" s="2">
-        <v>2</v>
-      </c>
-      <c r="E18" s="2">
-        <v>8</v>
-      </c>
-      <c r="F18" s="2">
-        <v>3</v>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|潢</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-潢</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">어</t>
         </is>
       </c>
       <c r="J18" s="4"/>
@@ -1279,23 +1240,26 @@
         <v>2</v>
       </c>
       <c r="E19" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F19" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|無</t>
+          <t xml:space="preserve">汰^</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="I19" s="2"/>
+          <t xml:space="preserve">汰^</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
       <c r="J19" s="4"/>
       <c r="K19" s="2"/>
     </row>
@@ -1315,26 +1279,22 @@
         <v>2</v>
       </c>
       <c r="E20" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F20" s="2">
         <v>4</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">두</t>
-        </is>
-      </c>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I20" s="2"/>
       <c r="J20" s="4"/>
       <c r="K20" s="2"/>
     </row>
@@ -1354,27 +1314,28 @@
         <v>2</v>
       </c>
       <c r="E21" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F21" s="2">
         <v>4</v>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑^</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑^</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">고</t>
-        </is>
-      </c>
-      <c r="J21" s="4"/>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I21" s="3"/>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△ 가 ▷ 모양</t>
+        </is>
+      </c>
       <c r="K21" s="2"/>
     </row>
     <row r="22">
@@ -1387,28 +1348,32 @@
         </is>
       </c>
       <c r="C22" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F22" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I22" s="2"/>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고</t>
+        </is>
+      </c>
       <c r="J22" s="4"/>
       <c r="K22" s="2"/>
     </row>
@@ -1428,24 +1393,24 @@
         <v>3</v>
       </c>
       <c r="E23" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" s="2">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구</t>
+          <t xml:space="preserve">운</t>
         </is>
       </c>
       <c r="J23" s="4"/>
@@ -1467,22 +1432,26 @@
         <v>3</v>
       </c>
       <c r="E24" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F24" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I24" s="2"/>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">임</t>
+        </is>
+      </c>
       <c r="J24" s="4"/>
       <c r="K24" s="2"/>
     </row>
@@ -1502,19 +1471,19 @@
         <v>3</v>
       </c>
       <c r="E25" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F25" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I25" s="2"/>
@@ -1537,26 +1506,22 @@
         <v>3</v>
       </c>
       <c r="E26" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F26" s="2">
         <v>2</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정</t>
-        </is>
-      </c>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I26" s="2"/>
       <c r="J26" s="4"/>
       <c r="K26" s="2"/>
     </row>
@@ -1576,24 +1541,24 @@
         <v>3</v>
       </c>
       <c r="E27" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F27" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢^</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢^</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">을</t>
+          <t xml:space="preserve">걸</t>
         </is>
       </c>
       <c r="J27" s="4"/>
@@ -1615,22 +1580,27 @@
         <v>3</v>
       </c>
       <c r="E28" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F28" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">潢|㴌</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I28" s="2"/>
+          <t xml:space="preserve">潢
+㴌</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
       <c r="J28" s="4"/>
       <c r="K28" s="2"/>
     </row>
@@ -1650,26 +1620,23 @@
         <v>3</v>
       </c>
       <c r="E29" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F29" s="2">
         <v>3</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢|無</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">엿</t>
-        </is>
-      </c>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="I29" s="2"/>
       <c r="J29" s="4"/>
       <c r="K29" s="2"/>
     </row>
@@ -1689,25 +1656,24 @@
         <v>3</v>
       </c>
       <c r="E30" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F30" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">었</t>
+          <t xml:space="preserve">두</t>
         </is>
       </c>
       <c r="J30" s="4"/>
@@ -1729,23 +1695,26 @@
         <v>3</v>
       </c>
       <c r="E31" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F31" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|無</t>
+          <t xml:space="preserve">南^</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="I31" s="2"/>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고</t>
+        </is>
+      </c>
       <c r="J31" s="4"/>
       <c r="K31" s="2"/>
     </row>
@@ -1765,27 +1734,28 @@
         <v>3</v>
       </c>
       <c r="E32" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F32" s="2">
         <v>4</v>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도</t>
-        </is>
-      </c>
-      <c r="J32" s="4"/>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I32" s="3"/>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△ 가 ▷ 모양</t>
+        </is>
+      </c>
       <c r="K32" s="2"/>
     </row>
     <row r="33">
@@ -1798,30 +1768,30 @@
         </is>
       </c>
       <c r="C33" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E33" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F33" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">다</t>
+          <t xml:space="preserve">구</t>
         </is>
       </c>
       <c r="J33" s="4"/>
@@ -1837,25 +1807,25 @@
         </is>
       </c>
       <c r="C34" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" s="2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F34" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I34" s="2"/>
@@ -1878,26 +1848,22 @@
         <v>4</v>
       </c>
       <c r="E35" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F35" s="2">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그</t>
-        </is>
-      </c>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I35" s="2"/>
       <c r="J35" s="4"/>
       <c r="K35" s="2"/>
     </row>
@@ -1917,22 +1883,26 @@
         <v>4</v>
       </c>
       <c r="E36" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F36" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I36" s="2"/>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정</t>
+        </is>
+      </c>
       <c r="J36" s="4"/>
       <c r="K36" s="2"/>
     </row>
@@ -1952,24 +1922,24 @@
         <v>4</v>
       </c>
       <c r="E37" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F37" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">㴌^</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">㴌^</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의</t>
+          <t xml:space="preserve">을</t>
         </is>
       </c>
       <c r="J37" s="4"/>
@@ -1991,26 +1961,22 @@
         <v>4</v>
       </c>
       <c r="E38" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F38" s="2">
         <v>2</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑^</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑^</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">말</t>
-        </is>
-      </c>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I38" s="2"/>
       <c r="J38" s="4"/>
       <c r="K38" s="2"/>
     </row>
@@ -2030,23 +1996,31 @@
         <v>4</v>
       </c>
       <c r="E39" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F39" s="2">
-        <v>2</v>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I39" s="2"/>
-      <c r="J39" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">엿</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 엿/맺?</t>
+        </is>
+      </c>
       <c r="K39" s="2"/>
     </row>
     <row r="40">
@@ -2065,24 +2039,25 @@
         <v>4</v>
       </c>
       <c r="E40" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F40" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑^</t>
+          <t xml:space="preserve">潢|㴌</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑^</t>
+          <t xml:space="preserve">潢
+㴌</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이</t>
+          <t xml:space="preserve">었</t>
         </is>
       </c>
       <c r="J40" s="4"/>
@@ -2104,26 +2079,23 @@
         <v>4</v>
       </c>
       <c r="E41" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F41" s="2">
         <v>3</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢|無</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부</t>
-        </is>
-      </c>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="I41" s="2"/>
       <c r="J41" s="4"/>
       <c r="K41" s="2"/>
     </row>
@@ -2143,24 +2115,24 @@
         <v>4</v>
       </c>
       <c r="E42" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F42" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">삼</t>
+          <t xml:space="preserve">도</t>
         </is>
       </c>
       <c r="J42" s="4"/>
@@ -2182,411 +2154,411 @@
         <v>4</v>
       </c>
       <c r="E43" s="2">
+        <v>11</v>
+      </c>
+      <c r="F43" s="2">
+        <v>4</v>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
+      <c r="J43" s="4"/>
+      <c r="K43" s="2"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2">
+        <v>1</v>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/석별가.png</t>
+        </is>
+      </c>
+      <c r="C44" s="2">
+        <v>4</v>
+      </c>
+      <c r="D44" s="2">
+        <v>4</v>
+      </c>
+      <c r="E44" s="2">
+        <v>12</v>
+      </c>
+      <c r="F44" s="2">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I44" s="3"/>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△ 가 ▷ 모양</t>
+        </is>
+      </c>
+      <c r="K44" s="2"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2">
+        <v>1</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/석별가.png</t>
+        </is>
+      </c>
+      <c r="C45" s="2">
+        <v>5</v>
+      </c>
+      <c r="D45" s="2">
+        <v>5</v>
+      </c>
+      <c r="E45" s="2">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그</t>
+        </is>
+      </c>
+      <c r="J45" s="4"/>
+      <c r="K45" s="2"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2">
+        <v>1</v>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/석별가.png</t>
+        </is>
+      </c>
+      <c r="C46" s="2">
+        <v>5</v>
+      </c>
+      <c r="D46" s="2">
+        <v>5</v>
+      </c>
+      <c r="E46" s="2">
+        <v>2</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I46" s="2"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="2"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2">
+        <v>1</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/석별가.png</t>
+        </is>
+      </c>
+      <c r="C47" s="2">
+        <v>5</v>
+      </c>
+      <c r="D47" s="2">
+        <v>5</v>
+      </c>
+      <c r="E47" s="2">
+        <v>3</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의</t>
+        </is>
+      </c>
+      <c r="J47" s="4"/>
+      <c r="K47" s="2"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2">
+        <v>1</v>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/석별가.png</t>
+        </is>
+      </c>
+      <c r="C48" s="2">
+        <v>5</v>
+      </c>
+      <c r="D48" s="2">
+        <v>5</v>
+      </c>
+      <c r="E48" s="2">
+        <v>4</v>
+      </c>
+      <c r="F48" s="2">
+        <v>2</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">말</t>
+        </is>
+      </c>
+      <c r="J48" s="4"/>
+      <c r="K48" s="2"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2">
+        <v>1</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/석별가.png</t>
+        </is>
+      </c>
+      <c r="C49" s="2">
+        <v>5</v>
+      </c>
+      <c r="D49" s="2">
+        <v>5</v>
+      </c>
+      <c r="E49" s="2">
+        <v>5</v>
+      </c>
+      <c r="F49" s="2">
+        <v>2</v>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I49" s="2"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="2"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2">
+        <v>1</v>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/석별가.png</t>
+        </is>
+      </c>
+      <c r="C50" s="2">
+        <v>5</v>
+      </c>
+      <c r="D50" s="2">
+        <v>5</v>
+      </c>
+      <c r="E50" s="2">
+        <v>6</v>
+      </c>
+      <c r="F50" s="2">
+        <v>2</v>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+      <c r="J50" s="4"/>
+      <c r="K50" s="2"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2">
+        <v>1</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/석별가.png</t>
+        </is>
+      </c>
+      <c r="C51" s="2">
+        <v>5</v>
+      </c>
+      <c r="D51" s="2">
+        <v>5</v>
+      </c>
+      <c r="E51" s="2">
+        <v>7</v>
+      </c>
+      <c r="F51" s="2">
+        <v>3</v>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부</t>
+        </is>
+      </c>
+      <c r="J51" s="4"/>
+      <c r="K51" s="2"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2">
+        <v>1</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/석별가.png</t>
+        </is>
+      </c>
+      <c r="C52" s="2">
+        <v>5</v>
+      </c>
+      <c r="D52" s="2">
+        <v>5</v>
+      </c>
+      <c r="E52" s="2">
+        <v>8</v>
+      </c>
+      <c r="F52" s="2">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|㴌</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+㴌</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">삼</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 삼/산?</t>
+        </is>
+      </c>
+      <c r="K52" s="2"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2">
+        <v>1</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/석별가.png</t>
+        </is>
+      </c>
+      <c r="C53" s="2">
+        <v>5</v>
+      </c>
+      <c r="D53" s="2">
+        <v>5</v>
+      </c>
+      <c r="E53" s="2">
         <v>9</v>
       </c>
-      <c r="F43" s="2">
-        <v>3</v>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="F53" s="2">
+        <v>3</v>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢|無</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I43" s="2"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="2"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2">
-        <v>1</v>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/석별가.png</t>
-        </is>
-      </c>
-      <c r="C44" s="2">
-        <v>4</v>
-      </c>
-      <c r="D44" s="2">
-        <v>4</v>
-      </c>
-      <c r="E44" s="2">
-        <v>10</v>
-      </c>
-      <c r="F44" s="2">
-        <v>4</v>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">말</t>
-        </is>
-      </c>
-      <c r="J44" s="4"/>
-      <c r="K44" s="2"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2">
-        <v>1</v>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/석별가.png</t>
-        </is>
-      </c>
-      <c r="C45" s="2">
-        <v>4</v>
-      </c>
-      <c r="D45" s="2">
-        <v>4</v>
-      </c>
-      <c r="E45" s="2">
-        <v>12</v>
-      </c>
-      <c r="F45" s="2">
-        <v>4</v>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">고</t>
-        </is>
-      </c>
-      <c r="J45" s="4"/>
-      <c r="K45" s="2"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2">
-        <v>1</v>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/석별가.png</t>
-        </is>
-      </c>
-      <c r="C46" s="2">
-        <v>5</v>
-      </c>
-      <c r="D46" s="2">
-        <v>5</v>
-      </c>
-      <c r="E46" s="2">
-        <v>1</v>
-      </c>
-      <c r="F46" s="2">
-        <v>1</v>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가</t>
-        </is>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">청림</t>
-        </is>
-      </c>
-      <c r="K46" s="2"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2">
-        <v>1</v>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/석별가.png</t>
-        </is>
-      </c>
-      <c r="C47" s="2">
-        <v>5</v>
-      </c>
-      <c r="D47" s="2">
-        <v>5</v>
-      </c>
-      <c r="E47" s="2">
-        <v>2</v>
-      </c>
-      <c r="F47" s="2">
-        <v>1</v>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세</t>
-        </is>
-      </c>
-      <c r="J47" s="4"/>
-      <c r="K47" s="2"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2">
-        <v>1</v>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/석별가.png</t>
-        </is>
-      </c>
-      <c r="C48" s="2">
-        <v>5</v>
-      </c>
-      <c r="D48" s="2">
-        <v>5</v>
-      </c>
-      <c r="E48" s="2">
-        <v>3</v>
-      </c>
-      <c r="F48" s="2">
-        <v>1</v>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I48" s="2"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="2"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2">
-        <v>1</v>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/석별가.png</t>
-        </is>
-      </c>
-      <c r="C49" s="2">
-        <v>5</v>
-      </c>
-      <c r="D49" s="2">
-        <v>5</v>
-      </c>
-      <c r="E49" s="2">
-        <v>4</v>
-      </c>
-      <c r="F49" s="2">
-        <v>2</v>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가</t>
-        </is>
-      </c>
-      <c r="J49" s="4"/>
-      <c r="K49" s="2"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2">
-        <v>1</v>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/석별가.png</t>
-        </is>
-      </c>
-      <c r="C50" s="2">
-        <v>5</v>
-      </c>
-      <c r="D50" s="2">
-        <v>5</v>
-      </c>
-      <c r="E50" s="2">
-        <v>5</v>
-      </c>
-      <c r="F50" s="2">
-        <v>2</v>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세</t>
-        </is>
-      </c>
-      <c r="J50" s="4"/>
-      <c r="K50" s="2"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2">
-        <v>1</v>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/석별가.png</t>
-        </is>
-      </c>
-      <c r="C51" s="2">
-        <v>5</v>
-      </c>
-      <c r="D51" s="2">
-        <v>5</v>
-      </c>
-      <c r="E51" s="2">
-        <v>6</v>
-      </c>
-      <c r="F51" s="2">
-        <v>2</v>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|無</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="I51" s="2"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="2"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2">
-        <v>1</v>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/석별가.png</t>
-        </is>
-      </c>
-      <c r="C52" s="2">
-        <v>5</v>
-      </c>
-      <c r="D52" s="2">
-        <v>5</v>
-      </c>
-      <c r="E52" s="2">
-        <v>7</v>
-      </c>
-      <c r="F52" s="2">
-        <v>3</v>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나</t>
-        </is>
-      </c>
-      <c r="J52" s="4"/>
-      <c r="K52" s="2"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2">
-        <v>1</v>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/석별가.png</t>
-        </is>
-      </c>
-      <c r="C53" s="2">
-        <v>5</v>
-      </c>
-      <c r="D53" s="2">
-        <v>5</v>
-      </c>
-      <c r="E53" s="2">
-        <v>8</v>
-      </c>
-      <c r="F53" s="2">
-        <v>3</v>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|潢</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-潢</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도</t>
-        </is>
-      </c>
+      <c r="I53" s="2"/>
       <c r="J53" s="4"/>
       <c r="K53" s="2"/>
     </row>
@@ -2606,25 +2578,24 @@
         <v>5</v>
       </c>
       <c r="E54" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F54" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|無</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-無</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가</t>
+          <t xml:space="preserve">말</t>
         </is>
       </c>
       <c r="J54" s="4"/>
@@ -2646,27 +2617,27 @@
         <v>5</v>
       </c>
       <c r="E55" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F55" s="2">
         <v>4</v>
       </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세</t>
-        </is>
-      </c>
-      <c r="J55" s="4"/>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I55" s="3"/>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">흐린 짧은 선 2개(–|–?)</t>
+        </is>
+      </c>
       <c r="K55" s="2"/>
     </row>
     <row r="56">
@@ -2685,22 +2656,26 @@
         <v>5</v>
       </c>
       <c r="E56" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F56" s="2">
         <v>4</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I56" s="2"/>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고</t>
+        </is>
+      </c>
       <c r="J56" s="4"/>
       <c r="K56" s="2"/>
     </row>
@@ -2714,33 +2689,33 @@
         </is>
       </c>
       <c r="C57" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D57" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E57" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F57" s="2">
-        <v>4</v>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I57" s="3"/>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">종지 동그라미로 봄</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
+      <c r="J57" s="4"/>
       <c r="K57" s="2"/>
     </row>
     <row r="58">
@@ -2759,22 +2734,26 @@
         <v>6</v>
       </c>
       <c r="E58" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58" s="2">
         <v>1</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="I58" s="2"/>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세</t>
+        </is>
+      </c>
       <c r="J58" s="4"/>
       <c r="K58" s="2"/>
     </row>
@@ -2794,19 +2773,19 @@
         <v>6</v>
       </c>
       <c r="E59" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F59" s="2">
         <v>1</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I59" s="2"/>
@@ -2829,22 +2808,26 @@
         <v>6</v>
       </c>
       <c r="E60" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F60" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I60" s="2"/>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
       <c r="J60" s="4"/>
       <c r="K60" s="2"/>
     </row>
@@ -2864,19 +2847,20 @@
         <v>6</v>
       </c>
       <c r="E61" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F61" s="2">
         <v>2</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">–|㴌</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">–
+㴌</t>
         </is>
       </c>
       <c r="I61" s="2"/>
@@ -2899,23 +2883,27 @@
         <v>6</v>
       </c>
       <c r="E62" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F62" s="2">
         <v>2</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|潢</t>
+          <t xml:space="preserve">潢|無</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-潢</t>
-        </is>
-      </c>
-      <c r="I62" s="2"/>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세</t>
+        </is>
+      </c>
       <c r="J62" s="4"/>
       <c r="K62" s="2"/>
     </row>
@@ -2935,23 +2923,26 @@
         <v>6</v>
       </c>
       <c r="E63" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F63" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|無</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="I63" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
       <c r="J63" s="4"/>
       <c r="K63" s="2"/>
     </row>
@@ -2971,22 +2962,26 @@
         <v>6</v>
       </c>
       <c r="E64" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F64" s="2">
         <v>3</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I64" s="2"/>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도</t>
+        </is>
+      </c>
       <c r="J64" s="4"/>
       <c r="K64" s="2"/>
     </row>
@@ -3006,22 +3001,27 @@
         <v>6</v>
       </c>
       <c r="E65" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F65" s="2">
         <v>3</v>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I65" s="2"/>
+          <t xml:space="preserve">–
+無</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
       <c r="J65" s="4"/>
       <c r="K65" s="2"/>
     </row>
@@ -3041,23 +3041,26 @@
         <v>6</v>
       </c>
       <c r="E66" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F66" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|無</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-無</t>
-        </is>
-      </c>
-      <c r="I66" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세</t>
+        </is>
+      </c>
       <c r="J66" s="4"/>
       <c r="K66" s="2"/>
     </row>
@@ -3077,19 +3080,19 @@
         <v>6</v>
       </c>
       <c r="E67" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F67" s="2">
         <v>4</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I67" s="2"/>
@@ -3112,66 +3115,31 @@
         <v>6</v>
       </c>
       <c r="E68" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F68" s="2">
         <v>4</v>
       </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I68" s="2"/>
-      <c r="J68" s="4"/>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="I68" s="3"/>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△ 가 ▷(D) 모양</t>
+        </is>
+      </c>
       <c r="K68" s="2"/>
     </row>
-    <row r="69">
-      <c r="A69" s="2">
-        <v>1</v>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/석별가.png</t>
-        </is>
-      </c>
-      <c r="C69" s="2">
-        <v>6</v>
-      </c>
-      <c r="D69" s="2">
-        <v>6</v>
-      </c>
-      <c r="E69" s="2">
-        <v>12</v>
-      </c>
-      <c r="F69" s="2">
-        <v>4</v>
-      </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I69" s="3"/>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">종지 동그라미로 봄</t>
-        </is>
-      </c>
-      <c r="K69" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K69"/>
+  <autoFilter ref="A1:K68"/>
 </worksheet>
 </file>
 
@@ -3196,7 +3164,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="55.19" customHeight="1">
+    <row r="2" ht="52.21" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3215,255 +3183,263 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="55.19" customHeight="1">
+    <row r="3" ht="52.21" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="E3" s="30" t="inlineStr">
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그</t>
+        </is>
+      </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구</t>
+        </is>
+      </c>
+      <c r="H3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고</t>
+        </is>
+      </c>
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">거</t>
+        </is>
+      </c>
+      <c r="L3" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G3" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그</t>
-        </is>
-      </c>
-      <c r="H3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I3" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">구</t>
-        </is>
-      </c>
-      <c r="J3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K3" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">고</t>
-        </is>
-      </c>
-      <c r="L3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M3" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">거</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="55.19" customHeight="1">
+      <c r="M3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="52.21" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="C4" s="31"/>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세</t>
+        </is>
+      </c>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="E4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="E4" s="23"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G4" s="31"/>
-      <c r="H4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I4" s="31"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="23" t="inlineStr">
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="G4" s="23"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M4" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">닌</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="55.19" customHeight="1">
+      <c r="K4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">년</t>
+        </is>
+      </c>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑^</t>
+        </is>
+      </c>
+      <c r="M4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">련</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52.21" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="33"/>
+      <c r="C5" s="24"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E5" s="33"/>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G5" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">의</t>
-        </is>
-      </c>
+      <c r="G5" s="24"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I5" s="33"/>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K5" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">은</t>
-        </is>
-      </c>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="I5" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">운</t>
+        </is>
+      </c>
+      <c r="J5" s="21"/>
+      <c r="K5" s="24"/>
       <c r="L5" s="21"/>
-      <c r="M5" s="33"/>
-    </row>
-    <row r="6" ht="55.19" customHeight="1">
+      <c r="M5" s="24"/>
+    </row>
+    <row r="6" ht="52.21" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C6" s="29"/>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가</t>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">말</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑^</t>
-        </is>
-      </c>
-      <c r="G6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">말</t>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정</t>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">임</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">임</t>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">금</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="M6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">금</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="55.19" customHeight="1">
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52.21" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢</t>
-        </is>
-      </c>
-      <c r="C7" s="31"/>
+㴌</t>
+        </is>
+      </c>
+      <c r="C7" s="23"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="E7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="E7" s="23"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">㴌^</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">을</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G7" s="31"/>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢^</t>
-        </is>
-      </c>
-      <c r="I7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">을</t>
-        </is>
-      </c>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K7" s="31"/>
-      <c r="L7" s="21"/>
-      <c r="M7" s="31"/>
-    </row>
-    <row r="8" ht="55.19" customHeight="1">
+      <c r="I7" s="23"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="M7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">님</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="52.21" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3471,237 +3447,248 @@
 無</t>
         </is>
       </c>
-      <c r="C8" s="33"/>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세</t>
+        </is>
+      </c>
       <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G8" s="24"/>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I8" s="24"/>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰^</t>
+        </is>
+      </c>
+      <c r="K8" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">년</t>
+        </is>
+      </c>
+      <c r="L8" s="21"/>
+      <c r="M8" s="24"/>
+    </row>
+    <row r="9" ht="52.21" customHeight="1">
+      <c r="A9" s="0"/>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부</t>
+        </is>
+      </c>
+      <c r="F9" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G9" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">엿</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">걸</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">돈</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52.21" customHeight="1">
+      <c r="A10" s="0"/>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+㴌</t>
+        </is>
+      </c>
+      <c r="E10" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">삼</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+㴌</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">었</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+㴌</t>
+        </is>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="K10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">절</t>
+        </is>
+      </c>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="M10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">별</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52.21" customHeight="1">
+      <c r="A11" s="0"/>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+無</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E8" s="33"/>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑^</t>
-        </is>
-      </c>
-      <c r="G8" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I8" s="33"/>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K8" s="33"/>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰^</t>
-        </is>
-      </c>
-      <c r="M8" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">면</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="55.19" customHeight="1">
-      <c r="A9" s="0"/>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나</t>
-        </is>
-      </c>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부</t>
-        </is>
-      </c>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">엿</t>
-        </is>
-      </c>
-      <c r="J9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">걸</t>
-        </is>
-      </c>
-      <c r="L9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="M9" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">돈</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="55.19" customHeight="1">
-      <c r="A10" s="0"/>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C10" s="31"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-潢</t>
-        </is>
-      </c>
-      <c r="E10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">삼</t>
-        </is>
-      </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-潢</t>
-        </is>
-      </c>
-      <c r="I10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">었</t>
-        </is>
-      </c>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-潢</t>
-        </is>
-      </c>
-      <c r="K10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">어</t>
-        </is>
-      </c>
-      <c r="L10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M10" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">질</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="55.19" customHeight="1">
-      <c r="A11" s="0"/>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-無</t>
-        </is>
-      </c>
-      <c r="C11" s="33"/>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="E11" s="24"/>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E11" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가</t>
-        </is>
-      </c>
-      <c r="F11" s="21" t="inlineStr">
+      <c r="G11" s="24"/>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G11" s="33"/>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="I11" s="33"/>
+      <c r="I11" s="24"/>
       <c r="J11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="K11" s="33"/>
-      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="M11" s="33" t="inlineStr">
+      <c r="K11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="55.19" customHeight="1">
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+姑</t>
+        </is>
+      </c>
+      <c r="M11" s="24"/>
+    </row>
+    <row r="12" ht="52.21" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="29"/>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세</t>
+        </is>
+      </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세</t>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">말</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -3709,9 +3696,9 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">말</t>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -3719,117 +3706,128 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도</t>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">두</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">汰^</t>
+        </is>
+      </c>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">두</t>
-        </is>
-      </c>
-      <c r="L12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰^</t>
-        </is>
-      </c>
-      <c r="M12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="55.19" customHeight="1">
+      <c r="M12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52.21" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="C13" s="23"/>
+      <c r="D13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E13" s="31"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="31"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
       <c r="H13" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="I13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="K13" s="23"/>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="M13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52.21" customHeight="1">
+      <c r="A14" s="0"/>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="C14" s="28"/>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I13" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑^</t>
-        </is>
-      </c>
-      <c r="K13" s="31" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="L13" s="21" t="inlineStr">
+      <c r="F14" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="G14" s="28"/>
+      <c r="H14" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I14" s="28"/>
+      <c r="J14" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="K14" s="28"/>
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M13" s="31"/>
-    </row>
-    <row r="14" ht="55.19" customHeight="1">
-      <c r="A14" s="0"/>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C14" s="34"/>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E14" s="34"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G14" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">고</t>
-        </is>
-      </c>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I14" s="33"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K14" s="33"/>
-      <c r="L14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="M14" s="34"/>
+      <c r="M14" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/석별가.xlsx
+++ b/sheets/민요/검수/석별가.xlsx
@@ -65,10 +65,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">

--- a/sheets/민요/검수/석별가.xlsx
+++ b/sheets/민요/검수/석별가.xlsx
@@ -3142,6 +3142,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -3158,10 +3161,10 @@
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="52.21" customHeight="1">
+    <row r="2" ht="51.95" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3180,7 +3183,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="52.21" customHeight="1">
+    <row r="3" ht="77.24" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3243,7 +3246,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="52.21" customHeight="1">
+    <row r="4" ht="77.24" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3290,7 +3293,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="52.21" customHeight="1">
+    <row r="5" ht="77.24" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3329,7 +3332,7 @@
       <c r="L5" s="21"/>
       <c r="M5" s="24"/>
     </row>
-    <row r="6" ht="52.21" customHeight="1">
+    <row r="6" ht="77.24" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3392,7 +3395,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="52.21" customHeight="1">
+    <row r="7" ht="77.24" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3436,7 +3439,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="52.21" customHeight="1">
+    <row r="8" ht="77.24" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3484,7 +3487,7 @@
       <c r="L8" s="21"/>
       <c r="M8" s="24"/>
     </row>
-    <row r="9" ht="52.21" customHeight="1">
+    <row r="9" ht="77.24" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3547,7 +3550,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="52.21" customHeight="1">
+    <row r="10" ht="77.24" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3613,7 +3616,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="52.21" customHeight="1">
+    <row r="11" ht="77.24" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3666,7 +3669,7 @@
       </c>
       <c r="M11" s="24"/>
     </row>
-    <row r="12" ht="52.21" customHeight="1">
+    <row r="12" ht="77.24" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3729,7 +3732,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="52.21" customHeight="1">
+    <row r="13" ht="77.24" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -3780,7 +3783,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="52.21" customHeight="1">
+    <row r="14" ht="77.24" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="25" t="inlineStr">
         <is>
@@ -3832,6 +3835,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/석별가.xlsx
+++ b/sheets/민요/검수/석별가.xlsx
@@ -3147,24 +3147,24 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="51.95" customHeight="true">
+    <row r="2" ht="48.19" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="77.24" customHeight="true">
+    <row r="3" ht="71.62" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="77.24" customHeight="true">
+    <row r="4" ht="71.62" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="77.24" customHeight="true">
+    <row r="5" ht="71.62" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
       <c r="L5" s="21"/>
       <c r="M5" s="24"/>
     </row>
-    <row r="6" ht="77.24" customHeight="true">
+    <row r="6" ht="71.62" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="77.24" customHeight="true">
+    <row r="7" ht="71.62" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="77.24" customHeight="true">
+    <row r="8" ht="71.62" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
       <c r="L8" s="21"/>
       <c r="M8" s="24"/>
     </row>
-    <row r="9" ht="77.24" customHeight="true">
+    <row r="9" ht="71.62" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="77.24" customHeight="true">
+    <row r="10" ht="71.62" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="77.24" customHeight="true">
+    <row r="11" ht="71.62" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="M11" s="24"/>
     </row>
-    <row r="12" ht="77.24" customHeight="true">
+    <row r="12" ht="71.62" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="77.24" customHeight="true">
+    <row r="13" ht="71.62" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="77.24" customHeight="true">
+    <row r="14" ht="71.62" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="25" t="inlineStr">
         <is>
@@ -3835,6 +3835,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="83"/>
 </worksheet>
 </file>